--- a/results/Int All Data 0.2/Rando_10_permute.xlsx
+++ b/results/Int All Data 0.2/Rando_10_permute.xlsx
@@ -440,837 +440,837 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.7598308919852328</v>
+        <v>0.7565063455738696</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>accx_pct_95</t>
+          <t>scl_energy</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.7601524353935929</v>
+        <v>0.7581504333915909</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>scl_n_sign_changes</t>
+          <t>scl_std</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.7601524353935929</v>
+        <v>0.7593303914847324</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>scl_sum</t>
+          <t>accz_ptp</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.7660856998477577</v>
+        <v>0.7598672627611534</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>bvp_mean</t>
+          <t>scl_svd_entropy</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.7660856998477577</v>
+        <v>0.7605467203537943</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>scl_mean</t>
+          <t>accz_lineintegral</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.7744094576892004</v>
+        <v>0.7611898071705145</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>bvp_lineintegral</t>
+          <t>bvp_mean</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.772088809066301</v>
+        <v>0.7611898071705145</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>accx_iqr</t>
+          <t>accy_rms</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.773089810067302</v>
+        <v>0.7543617572556479</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>accz_energy</t>
+          <t>accy_peaks</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.7779857027445451</v>
+        <v>0.7538612567551475</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_below_mean</t>
+          <t>scr_entropy</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.7784862032450457</v>
+        <v>0.7541828001635076</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>bvp_min</t>
+          <t>scr_svd_entropy</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.7773062451519044</v>
+        <v>0.7549684732964477</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>scr_kurtosis</t>
+          <t>bvp_peaks</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.7784498324691251</v>
+        <v>0.7556115601131679</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>scr_perm_entropy</t>
+          <t>scl_ptp</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.7784498324691251</v>
+        <v>0.756934104522529</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>accz_n_above_mean</t>
+          <t>scr_n_sign_changes</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.7784498324691251</v>
+        <v>0.756934104522529</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>scl_kurtosis</t>
+          <t>hrv_pct_95</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.7784498324691251</v>
+        <v>0.7557905172053082</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>scl_peaks</t>
+          <t>accy_std</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.7774852022440446</v>
+        <v>0.7614386090270335</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>scl_skewness</t>
+          <t>accz_pct_5</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.7774852022440446</v>
+        <v>0.7614386090270335</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>scr_ptp</t>
+          <t>accz_entropy</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.7860606587294691</v>
+        <v>0.7607955222103132</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr</t>
+          <t>bvp_ptp</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.7853477271483702</v>
+        <v>0.75714943239059</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>scr_max</t>
+          <t>hrv_energy</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.7888847046403317</v>
+        <v>0.7592576499328911</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_95</t>
+          <t>accz_skewness</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.7864549436896704</v>
+        <v>0.7625821963442543</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>accz_iqr</t>
+          <t>bvp_lineintegral</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.7840950275033876</v>
+        <v>0.7649421125305369</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_5</t>
+          <t>hrv_iqr_5_95</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.7837734840950275</v>
+        <v>0.761939109527534</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>scr_energy</t>
+          <t>accx_pct_5</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.7929556566212514</v>
+        <v>0.7546105591121668</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>hrv_entropy</t>
+          <t>bvp_std</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.7953155728075343</v>
+        <v>0.7556115601131679</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>scr_n_sign_changes</t>
+          <t>hrv_pct_5</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.7953155728075343</v>
+        <v>0.7573283894827303</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>accy_entropy</t>
+          <t>bvp_iqr</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.7953155728075343</v>
+        <v>0.7600098490773732</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>bvp_std</t>
+          <t>accy_perm_entropy</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.7929556566212514</v>
+        <v>0.7596155641171718</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>scr_sum</t>
+          <t>hrv_n_below_mean</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.7984218945633736</v>
+        <v>0.7609017377506123</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_95</t>
+          <t>accx_peaks</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.8013186820260776</v>
+        <v>0.7594002362491108</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>scl_min</t>
+          <t>hrv_mean</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.800602853657516</v>
+        <v>0.7599007367496113</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>accz_pct_5</t>
+          <t>scl_iqr_5_95</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.8032115717003177</v>
+        <v>0.7604012372501119</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>accy_iqr</t>
+          <t>accx_ptp</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.7978122817351113</v>
+        <v>0.7637621544373956</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>bvp_max</t>
+          <t>accz_energy</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.7990620845926313</v>
+        <v>0.7592576499328911</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr_5_95</t>
+          <t>accy_mean</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.798418997775911</v>
+        <v>0.7567551474303886</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>accy_kurtosis</t>
+          <t>accy_n_sign_changes</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.7987405411842712</v>
+        <v>0.7606165651181729</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>hrv_peaks</t>
+          <t>accy_energy</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.7987405411842712</v>
+        <v>0.7409908300583541</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>hrv_mean</t>
+          <t>bvp_energy</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.7995625850931317</v>
+        <v>0.7354489537769281</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>bvp_ptp</t>
+          <t>accx_sum</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.7995625850931317</v>
+        <v>0.7218263279356527</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>accz_sum</t>
+          <t>hrv_min</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.805468169133764</v>
+        <v>0.7377361284113695</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>scr_rms</t>
+          <t>accx_n_below_mean</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.8073974295839248</v>
+        <v>0.7410272008342749</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>accx_sum</t>
+          <t>scr_pct_5</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.8060719883871009</v>
+        <v>0.740884614518055</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr_5_95</t>
+          <t>scr_perm_entropy</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.8066787044279006</v>
+        <v>0.739883613517054</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>hrv_skewness</t>
+          <t>accx_n_above_mean</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.8066787044279006</v>
+        <v>0.737881611515052</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>bvp_perm_entropy</t>
+          <t>hrv_peaks</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.8042824174656972</v>
+        <v>0.7413851150185555</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>accy_iqr_5_95</t>
+          <t>accz_min</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.8031024593725559</v>
+        <v>0.7457106624309197</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>accy_std</t>
+          <t>accx_iqr</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.8020650875956342</v>
+        <v>0.7446034458896196</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>accy_svd_entropy</t>
+          <t>bvp_iqr_5_95</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.8004209997779129</v>
+        <v>0.7399199842929747</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr</t>
+          <t>scl_skewness</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.8013856300029933</v>
+        <v>0.7399199842929747</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>hrv_min</t>
+          <t>scl_perm_entropy</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.8048192887421184</v>
+        <v>0.7355944368806104</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>accz_std</t>
+          <t>accy_n_below_mean</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.8045704868855994</v>
+        <v>0.7380969393831129</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>accz_lineintegral</t>
+          <t>accx_rms</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.8053226860300815</v>
+        <v>0.7227240101838173</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>accz_svd_entropy</t>
+          <t>accx_entropy</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.8033934255799208</v>
+        <v>0.7244044687774591</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>accy_lineintegral</t>
+          <t>scr_lineintegral</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.8031417269359391</v>
+        <v>0.7263701000035405</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>scl_entropy</t>
+          <t>scl_peaks</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.7998200773120387</v>
+        <v>0.7263701000035405</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>hrv_ptp</t>
+          <t>scl_entropy</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.8086414388665193</v>
+        <v>0.721759379958737</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>accy_rms</t>
+          <t>hrv_n_above_mean</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.797202668906849</v>
+        <v>0.721759379958737</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>hrv_rms</t>
+          <t>accz_pct_95</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.8015282163192131</v>
+        <v>0.7290180856097255</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>accx_perm_entropy</t>
+          <t>bvp_n_sign_changes</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.8016344318595123</v>
+        <v>0.7344872203393104</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>scl_svd_entropy</t>
+          <t>bvp_max</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.8027780191767331</v>
+        <v>0.7308775012955078</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>bvp_entropy</t>
+          <t>accz_kurtosis</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.8027780191767331</v>
+        <v>0.7345570651036888</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>accx_max</t>
+          <t>accx_pct_95</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.8027780191767331</v>
+        <v>0.7273347302286208</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>hrv_kurtosis</t>
+          <t>bvp_entropy</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.8030995625850932</v>
+        <v>0.7273347302286208</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>accy_skewness</t>
+          <t>scr_n_below_mean</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.8027780191767331</v>
+        <v>0.7273347302286208</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>accy_sum</t>
+          <t>accx_n_sign_changes</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.8023837342165316</v>
+        <v>0.7289089732819636</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>bvp_kurtosis</t>
+          <t>accx_skewness</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.8012401468993109</v>
+        <v>0.7319119762849666</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>scl_n_above_mean</t>
+          <t>accz_iqr</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.8018832337160311</v>
+        <v>0.7094592985268227</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>accx_n_above_mean</t>
+          <t>hrv_rms</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.8023837342165316</v>
+        <v>0.6983755459639704</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>scr_n_above_mean</t>
+          <t>bvp_sum</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.8018832337160311</v>
+        <v>0.6983755459639704</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>accx_peaks</t>
+          <t>scl_min</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.804134037574552</v>
+        <v>0.6980511057681476</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>scr_n_below_mean</t>
+          <t>scl_pct_95</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.804134037574552</v>
+        <v>0.7022675408527499</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>accx_rms</t>
+          <t>bvp_skewness</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.8018439661526479</v>
+        <v>0.7033049126296715</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>scr_peaks</t>
+          <t>hrv_entropy</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.8024870529693682</v>
+        <v>0.7088831596870182</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>hrv_lineintegral</t>
+          <t>scl_mean</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.7993778344260659</v>
+        <v>0.712168438534998</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>accz_skewness</t>
+          <t>accz_n_above_mean</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.7987711183852663</v>
+        <v>0.7111310667580764</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_sign_changes</t>
+          <t>accz_n_below_mean</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.8000936627946275</v>
+        <v>0.7101300657570754</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>scr_mean</t>
+          <t>accy_min</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.8045254257472907</v>
+        <v>0.7096295652565749</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr</t>
+          <t>hrv_std</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.802165509561008</v>
+        <v>0.7056255612525709</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_above_mean</t>
+          <t>accx_energy</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.8024870529693682</v>
+        <v>0.6945083347012607</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>accz_iqr_5_95</t>
+          <t>hrv_max</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.8052412541158522</v>
+        <v>0.7075213477142738</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>accx_pct_5</t>
+          <t>scr_iqr</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.7949431746859399</v>
+        <v>0.7093443926241354</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>scl_energy</t>
+          <t>accz_peaks</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.7941938723289206</v>
+        <v>0.7091683323194578</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>bvp_skewness</t>
+          <t>scl_lineintegral</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.7931928713279195</v>
+        <v>0.7071299595415351</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>accx_n_below_mean</t>
+          <t>accy_n_above_mean</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.7889735394558546</v>
+        <v>0.7121349645465401</v>
       </c>
     </row>
     <row r="86">
@@ -1280,707 +1280,707 @@
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.7885094097312746</v>
+        <v>0.707809417134176</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>scr_svd_entropy</t>
+          <t>scr_ptp</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.7975518927287416</v>
+        <v>0.7108822649015576</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>accz_entropy</t>
+          <t>accy_max</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.8005548957317445</v>
+        <v>0.7105243507172767</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_5</t>
+          <t>accy_skewness</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.7983375658616816</v>
+        <v>0.7093443926241354</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>accy_pct_95</t>
+          <t>bvp_rms</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.7183273305459801</v>
+        <v>0.7150288552217813</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="1" t="inlineStr">
         <is>
-          <t>accy_n_above_mean</t>
+          <t>accy_kurtosis</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>0.7206872467322628</v>
+        <v>0.7150288552217813</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="1" t="inlineStr">
         <is>
-          <t>scl_perm_entropy</t>
+          <t>accz_svd_entropy</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>0.7201867462317624</v>
+        <v>0.7140307510082429</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="1" t="inlineStr">
         <is>
-          <t>hrv_energy</t>
+          <t>accz_perm_entropy</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>0.720544660416043</v>
+        <v>0.7230004924538687</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="1" t="inlineStr">
         <is>
-          <t>accx_min</t>
+          <t>accy_sum</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>0.71597031114716</v>
+        <v>0.7039814734348496</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="1" t="inlineStr">
         <is>
-          <t>accz_peaks</t>
+          <t>accx_lineintegral</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>0.7290196949360936</v>
+        <v>0.710166436532996</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="1" t="inlineStr">
         <is>
-          <t>accy_max</t>
+          <t>hrv_svd_entropy</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>0.698416422853722</v>
+        <v>0.7239316486904911</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="1" t="inlineStr">
         <is>
-          <t>accz_ptp</t>
+          <t>scr_min</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>0.6972364647605805</v>
+        <v>0.7239316486904911</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="1" t="inlineStr">
         <is>
-          <t>hrv_max</t>
+          <t>bvp_pct_95</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>0.704743972268088</v>
+        <v>0.7217870603722694</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="1" t="inlineStr">
         <is>
-          <t>scr_std</t>
+          <t>scl_kurtosis</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>0.7229045766023258</v>
+        <v>0.7224665179649102</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="1" t="inlineStr">
         <is>
-          <t>accx_lineintegral</t>
+          <t>scl_rms</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>0.7252644927886085</v>
+        <v>0.7184625139609062</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="1" t="inlineStr">
         <is>
-          <t>scl_max</t>
+          <t>scr_skewness</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>0.7202594877836035</v>
+        <v>0.7184625139609062</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="1" t="inlineStr">
         <is>
-          <t>bvp_sum</t>
+          <t>bvp_n_below_mean</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>0.7202594877836035</v>
+        <v>0.7186749450415045</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="1" t="inlineStr">
         <is>
-          <t>accx_kurtosis</t>
+          <t>hrv_iqr</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>0.7212604887846046</v>
+        <v>0.7106669370334966</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="1" t="inlineStr">
         <is>
-          <t>accy_energy</t>
+          <t>scl_n_sign_changes</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>0.6295597848652511</v>
+        <v>0.7106669370334966</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="1" t="inlineStr">
         <is>
-          <t>accy_mean</t>
+          <t>accx_svd_entropy</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>0.6170472723527386</v>
+        <v>0.7098448931246359</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="1" t="inlineStr">
         <is>
-          <t>accz_pct_95</t>
+          <t>scr_energy</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>0.6402885200312853</v>
+        <v>0.7106276694701132</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="1" t="inlineStr">
         <is>
-          <t>accy_ptp</t>
+          <t>accz_max</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>0.6177296267328422</v>
+        <v>0.7293731030065436</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="1" t="inlineStr">
         <is>
-          <t>accx_entropy</t>
+          <t>scr_std</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>0.6177296267328422</v>
+        <v>0.7392012591369505</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="1" t="inlineStr">
         <is>
-          <t>accx_ptp</t>
+          <t>hrv_sum</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>0.62541609133249</v>
+        <v>0.734481426764385</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="1" t="inlineStr">
         <is>
-          <t>accx_mean</t>
+          <t>bvp_kurtosis</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>0.6344643679048824</v>
+        <v>0.7335138997518419</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="1" t="inlineStr">
         <is>
-          <t>scl_n_below_mean</t>
+          <t>scl_n_above_mean</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>0.6346433249970227</v>
+        <v>0.7331923563434817</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="1" t="inlineStr">
         <is>
-          <t>bvp_rms</t>
+          <t>accx_std</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>0.6441921020699155</v>
+        <v>0.7363044716742466</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="1" t="inlineStr">
         <is>
-          <t>accx_svd_entropy</t>
+          <t>scr_pct_95</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>0.6439069294374761</v>
+        <v>0.7452014715680311</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="1" t="inlineStr">
         <is>
-          <t>accz_perm_entropy</t>
+          <t>accy_entropy</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>0.6127333120902253</v>
+        <v>0.7476312325186922</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="1" t="inlineStr">
         <is>
-          <t>accy_n_sign_changes</t>
+          <t>accx_min</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>0.6132701833666464</v>
+        <v>0.7463086881093313</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="1" t="inlineStr">
         <is>
-          <t>accx_n_sign_changes</t>
+          <t>accz_sum</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>0.6127696828661459</v>
+        <v>0.7076449439793491</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="1" t="inlineStr">
         <is>
-          <t>scl_ptp</t>
+          <t>accx_perm_entropy</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>0.6149841159487461</v>
+        <v>0.690918893169697</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="1" t="inlineStr">
         <is>
-          <t>bvp_energy</t>
+          <t>accy_iqr</t>
         </is>
       </c>
       <c r="B118" t="n">
-        <v>0.6162004448178082</v>
+        <v>0.7056181583512773</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="1" t="inlineStr">
         <is>
-          <t>accz_n_sign_changes</t>
+          <t>scr_iqr_5_95</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>0.6180598605035904</v>
+        <v>0.7051176578507767</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="1" t="inlineStr">
         <is>
-          <t>bvp_peaks</t>
+          <t>bvp_perm_entropy</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>0.600078213261493</v>
+        <v>0.6997183678855705</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="1" t="inlineStr">
         <is>
-          <t>accy_perm_entropy</t>
+          <t>accz_iqr_5_95</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>0.6101944388118021</v>
+        <v>0.6916463086881093</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr_5_95</t>
+          <t>accz_rms</t>
         </is>
       </c>
       <c r="B122" t="n">
-        <v>0.6099762141562785</v>
+        <v>0.6956342194284317</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="1" t="inlineStr">
         <is>
-          <t>accy_n_below_mean</t>
+          <t>bvp_pct_5</t>
         </is>
       </c>
       <c r="B123" t="n">
-        <v>0.6095120844316986</v>
+        <v>0.674521466804425</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="1" t="inlineStr">
         <is>
-          <t>accx_energy</t>
+          <t>scr_rms</t>
         </is>
       </c>
       <c r="B124" t="n">
-        <v>0.5809806591157074</v>
+        <v>0.6683117200802088</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_5</t>
+          <t>bvp_min</t>
         </is>
       </c>
       <c r="B125" t="n">
-        <v>0.579445683625748</v>
+        <v>0.663142241920377</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_above_mean</t>
+          <t>scl_sum</t>
         </is>
       </c>
       <c r="B126" t="n">
-        <v>0.5794791576142059</v>
+        <v>0.6639279150533171</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="1" t="inlineStr">
         <is>
-          <t>scl_std</t>
+          <t>hrv_kurtosis</t>
         </is>
       </c>
       <c r="B127" t="n">
-        <v>0.5801222444309261</v>
+        <v>0.6639279150533171</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_sign_changes</t>
+          <t>bvp_n_above_mean</t>
         </is>
       </c>
       <c r="B128" t="n">
-        <v>0.5801222444309261</v>
+        <v>0.637103019418132</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="1" t="inlineStr">
         <is>
-          <t>accz_mean</t>
+          <t>accx_mean</t>
         </is>
       </c>
       <c r="B129" t="n">
-        <v>0.5878608512049026</v>
+        <v>0.6742086137584531</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="1" t="inlineStr">
         <is>
-          <t>scl_lineintegral</t>
+          <t>hrv_lineintegral</t>
         </is>
       </c>
       <c r="B130" t="n">
-        <v>0.5886494211253054</v>
+        <v>0.6873716159889793</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_95</t>
+          <t>hrv_ptp</t>
         </is>
       </c>
       <c r="B131" t="n">
-        <v>0.6011954076262758</v>
+        <v>0.6867314259597218</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="1" t="inlineStr">
         <is>
-          <t>accy_min</t>
+          <t>accy_lineintegral</t>
         </is>
       </c>
       <c r="B132" t="n">
-        <v>0.5820949566930274</v>
+        <v>0.6809014802583935</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="1" t="inlineStr">
         <is>
-          <t>scr_entropy</t>
+          <t>hrv_perm_entropy</t>
         </is>
       </c>
       <c r="B133" t="n">
-        <v>0.5815944561925269</v>
+        <v>0.6823666109839743</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="1" t="inlineStr">
         <is>
-          <t>hrv_sum</t>
+          <t>bvp_svd_entropy</t>
         </is>
       </c>
       <c r="B134" t="n">
-        <v>0.5824470773023828</v>
+        <v>0.6809014802583935</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="1" t="inlineStr">
         <is>
-          <t>accx_skewness</t>
+          <t>scr_max</t>
         </is>
       </c>
       <c r="B135" t="n">
-        <v>0.5817312489338213</v>
+        <v>0.685976330027777</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="1" t="inlineStr">
         <is>
-          <t>scr_min</t>
+          <t>accy_pct_95</t>
         </is>
       </c>
       <c r="B136" t="n">
-        <v>0.5817312489338213</v>
+        <v>0.629595833775898</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="1" t="inlineStr">
         <is>
-          <t>accy_pct_5</t>
+          <t>accx_kurtosis</t>
         </is>
       </c>
       <c r="B137" t="n">
-        <v>0.565287473969146</v>
+        <v>0.6308820074093386</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="1" t="inlineStr">
         <is>
-          <t>bvp_svd_entropy</t>
+          <t>accy_svd_entropy</t>
         </is>
       </c>
       <c r="B138" t="n">
-        <v>0.5599609255557809</v>
+        <v>0.6275909349864334</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="1" t="inlineStr">
         <is>
-          <t>accz_min</t>
+          <t>hrv_n_sign_changes</t>
         </is>
       </c>
       <c r="B139" t="n">
-        <v>0.5273556514714071</v>
+        <v>0.6275909349864334</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_5</t>
+          <t>accy_pct_5</t>
         </is>
       </c>
       <c r="B140" t="n">
-        <v>0.5197200415849934</v>
+        <v>0.6028118150304645</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="1" t="inlineStr">
         <is>
-          <t>accx_std</t>
+          <t>accz_mean</t>
         </is>
       </c>
       <c r="B141" t="n">
-        <v>0.5113119550418586</v>
+        <v>0.5121111465162912</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="1" t="inlineStr">
         <is>
-          <t>accz_kurtosis</t>
+          <t>scr_sum</t>
         </is>
       </c>
       <c r="B142" t="n">
-        <v>0.5084180643666174</v>
+        <v>0.5150050371915323</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="1" t="inlineStr">
         <is>
-          <t>scl_rms</t>
+          <t>scl_n_below_mean</t>
         </is>
       </c>
       <c r="B143" t="n">
-        <v>0.5131349999517202</v>
+        <v>0.5033960005021099</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="1" t="inlineStr">
         <is>
-          <t>scr_skewness</t>
+          <t>scl_iqr</t>
         </is>
       </c>
       <c r="B144" t="n">
-        <v>0.5117426107779806</v>
+        <v>0.5003289463096537</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="1" t="inlineStr">
         <is>
-          <t>accz_n_below_mean</t>
+          <t>scr_peaks</t>
         </is>
       </c>
       <c r="B145" t="n">
-        <v>0.5130287844114211</v>
+        <v>0.5003289463096537</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr_5_95</t>
+          <t>scl_pct_5</t>
         </is>
       </c>
       <c r="B146" t="n">
-        <v>0.5154250713736245</v>
+        <v>0.4999040841484572</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="1" t="inlineStr">
         <is>
-          <t>accz_rms</t>
+          <t>accz_n_sign_changes</t>
         </is>
       </c>
       <c r="B147" t="n">
-        <v>0.4874549790948505</v>
+        <v>0.4908587043635275</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_95</t>
+          <t>scr_kurtosis</t>
         </is>
       </c>
       <c r="B148" t="n">
-        <v>0.4993186112157173</v>
+        <v>0.4908587043635275</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="1" t="inlineStr">
         <is>
-          <t>hrv_svd_entropy</t>
+          <t>accy_ptp</t>
         </is>
       </c>
       <c r="B149" t="n">
-        <v>0.5051543504919711</v>
+        <v>0.4970130902606786</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="1" t="inlineStr">
         <is>
-          <t>accy_peaks</t>
+          <t>scl_max</t>
         </is>
       </c>
       <c r="B150" t="n">
-        <v>0.5063343085851124</v>
+        <v>0.4970130902606786</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_below_mean</t>
+          <t>scr_mean</t>
         </is>
       </c>
       <c r="B151" t="n">
-        <v>0.4818039904856625</v>
+        <v>0.4967308144157019</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="1" t="inlineStr">
         <is>
-          <t>accz_max</t>
+          <t>accz_std</t>
         </is>
       </c>
       <c r="B152" t="n">
-        <v>0.5077714370318872</v>
+        <v>0.496406374219879</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="1" t="inlineStr">
         <is>
-          <t>hrv_perm_entropy</t>
+          <t>accy_iqr_5_95</t>
         </is>
       </c>
       <c r="B153" t="n">
-        <v>0.5076681182790508</v>
+        <v>0.4942981566775779</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="1" t="inlineStr">
         <is>
-          <t>hrv_std</t>
+          <t>hrv_skewness</t>
         </is>
       </c>
       <c r="B154" t="n">
-        <v>0.5099829733270247</v>
+        <v>0.4942981566775779</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="1" t="inlineStr">
         <is>
-          <t>scr_lineintegral</t>
+          <t>accx_max</t>
         </is>
       </c>
       <c r="B155" t="n">
-        <v>0.5086633257051264</v>
+        <v>0.4949412434942982</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr</t>
+          <t>scr_n_above_mean</t>
         </is>
       </c>
       <c r="B156" t="n">
-        <v>0.5118816565761903</v>
+        <v>0.4953718992304201</v>
       </c>
     </row>
   </sheetData>
